--- a/data/trans_camb/IP16A02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 32,31</t>
+          <t>-19,15; 35,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 35,34</t>
+          <t>-18,19; 37,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,49; 19,39</t>
+          <t>-34,39; 17,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 20,36</t>
+          <t>-36,87; 19,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,82; 15,77</t>
+          <t>-41,3; 16,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 9,89</t>
+          <t>-49,68; 7,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 19,44</t>
+          <t>-19,11; 21,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 17,47</t>
+          <t>-21,6; 18,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 5,5</t>
+          <t>-37,68; 4,06</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,36; 279,88</t>
+          <t>-50,74; 333,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,7; 308,34</t>
+          <t>-44,84; 332,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-75,61; 178,0</t>
+          <t>-78,68; 132,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,71; 68,23</t>
+          <t>-55,71; 66,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,87; 49,15</t>
+          <t>-59,53; 52,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,27; 32,67</t>
+          <t>-76,14; 33,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,11; 73,26</t>
+          <t>-39,19; 82,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 66,23</t>
+          <t>-41,99; 70,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,97; 22,49</t>
+          <t>-70,05; 20,0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 44,21</t>
+          <t>3,03; 42,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 34,97</t>
+          <t>-4,57; 34,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 58,39</t>
+          <t>-20,92; 58,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 40,94</t>
+          <t>-1,97; 39,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 43,54</t>
+          <t>-4,09; 41,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,16; 52,45</t>
+          <t>12,71; 53,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 36,99</t>
+          <t>9,47; 37,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 32,73</t>
+          <t>1,15; 32,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 46,66</t>
+          <t>-5,95; 47,83</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 560,13</t>
+          <t>6,69; 616,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 492,52</t>
+          <t>-17,3; 460,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 508,81</t>
+          <t>-47,58; 490,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 303,22</t>
+          <t>-8,35; 297,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 328,77</t>
+          <t>-12,74; 303,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 413,82</t>
+          <t>30,91; 430,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,45; 266,19</t>
+          <t>30,24; 266,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 239,54</t>
+          <t>3,6; 241,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 281,24</t>
+          <t>-3,29; 290,11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 60,6</t>
+          <t>9,9; 62,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 49,02</t>
+          <t>-13,35; 47,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 37,15</t>
+          <t>-13,0; 36,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-32,92; 25,27</t>
+          <t>-28,38; 28,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 23,36</t>
+          <t>-41,22; 27,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,04; -4,17</t>
+          <t>-55,83; -4,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 37,79</t>
+          <t>-1,4; 38,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 29,22</t>
+          <t>-20,73; 27,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 12,13</t>
+          <t>-26,8; 10,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,45; 913,76</t>
+          <t>18,15; 969,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,77; 897,61</t>
+          <t>-55,52; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,19; 587,89</t>
+          <t>-46,27; 639,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,64; 121,18</t>
+          <t>-50,4; 147,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,68; 121,4</t>
+          <t>-81,07; 162,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-93,07; 4,78</t>
+          <t>-93,15; 1,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 210,37</t>
+          <t>-5,02; 243,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,54; 158,73</t>
+          <t>-54,51; 152,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,4; 86,14</t>
+          <t>-63,48; 71,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,19; 21,49</t>
+          <t>-29,97; 19,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 27,21</t>
+          <t>-23,39; 26,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 38,78</t>
+          <t>-24,89; 38,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 22,27</t>
+          <t>-38,65; 19,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 18,11</t>
+          <t>-32,46; 17,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 55,09</t>
+          <t>-9,28; 56,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 14,71</t>
+          <t>-24,3; 13,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 15,43</t>
+          <t>-19,03; 14,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 39,91</t>
+          <t>-8,19; 38,68</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 82,1</t>
+          <t>-54,15; 72,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 111,49</t>
+          <t>-39,3; 102,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 132,06</t>
+          <t>-43,98; 146,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 88,05</t>
+          <t>-68,71; 78,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 67,9</t>
+          <t>-58,07; 66,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 218,65</t>
+          <t>-17,07; 238,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,31; 46,71</t>
+          <t>-47,28; 43,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 50,84</t>
+          <t>-37,01; 49,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 121,68</t>
+          <t>-15,76; 120,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,18; 70,19</t>
+          <t>16,35; 67,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 54,13</t>
+          <t>-14,22; 53,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,3; 68,95</t>
+          <t>6,41; 67,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 41,78</t>
+          <t>-28,52; 42,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 41,83</t>
+          <t>-34,55; 45,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 41,52</t>
+          <t>-33,86; 42,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,45; 50,08</t>
+          <t>5,78; 48,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 36,7</t>
+          <t>-16,09; 34,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 45,79</t>
+          <t>-5,25; 44,92</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>27,82; —</t>
+          <t>35,74; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-77,02; —</t>
+          <t>-97,01; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5,31; —</t>
+          <t>-5,03; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-50,72; 423,97</t>
+          <t>-49,41; 437,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,88; 403,38</t>
+          <t>-74,74; 397,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-59,99; 309,32</t>
+          <t>-59,39; 325,08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,89; 543,43</t>
+          <t>12,81; 420,95</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,7; 315,22</t>
+          <t>-45,64; 283,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 382,61</t>
+          <t>-13,01; 420,75</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 24,8</t>
+          <t>-37,01; 25,9</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-50,98; 8,36</t>
+          <t>-54,11; 4,48</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 25,69</t>
+          <t>-45,46; 21,07</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-32,43; 26,96</t>
+          <t>-34,64; 30,33</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-59,78; -5,1</t>
+          <t>-58,01; -1,08</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 25,12</t>
+          <t>-38,65; 27,27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 20,57</t>
+          <t>-23,11; 19,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-48,79; -8,19</t>
+          <t>-47,12; -7,14</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 15,19</t>
+          <t>-28,05; 17,98</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-73,2; 114,36</t>
+          <t>-69,5; 134,75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 100,46</t>
+          <t>-100,0; 59,46</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-83,12; 157,48</t>
+          <t>-84,99; 114,74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 125,41</t>
+          <t>-57,69; 127,59</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 33,42</t>
+          <t>-100,0; 71,46</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-59,64; 113,84</t>
+          <t>-61,8; 105,33</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-44,78; 92,65</t>
+          <t>-46,52; 71,42</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-93,12; -17,27</t>
+          <t>-93,14; -22,72</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-58,86; 52,7</t>
+          <t>-55,61; 72,49</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 14,32</t>
+          <t>-30,64; 13,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 27,47</t>
+          <t>-27,73; 24,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 33,02</t>
+          <t>-13,99; 31,84</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 5,65</t>
+          <t>-38,02; 4,02</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 35,01</t>
+          <t>-21,05; 31,89</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 24,09</t>
+          <t>-19,75; 23,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 5,22</t>
+          <t>-26,87; 3,71</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 22,24</t>
+          <t>-13,05; 23,07</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 22,46</t>
+          <t>-10,09; 22,09</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 46,96</t>
+          <t>-50,22; 39,12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 75,76</t>
+          <t>-46,44; 63,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 97,07</t>
+          <t>-22,05; 90,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-69,45; 26,83</t>
+          <t>-72,29; 17,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,76; 112,64</t>
+          <t>-43,84; 104,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 81,97</t>
+          <t>-38,33; 78,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-51,89; 14,11</t>
+          <t>-51,3; 10,32</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 59,43</t>
+          <t>-24,27; 62,63</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 61,26</t>
+          <t>-18,9; 64,09</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-29,93; 11,9</t>
+          <t>-28,96; 13,1</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 24,22</t>
+          <t>-15,34; 23,89</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 41,51</t>
+          <t>-20,33; 38,5</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 12,57</t>
+          <t>-29,23; 10,33</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 7,0</t>
+          <t>-29,09; 7,22</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 31,3</t>
+          <t>-22,35; 32,96</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 4,15</t>
+          <t>-22,6; 5,76</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 9,26</t>
+          <t>-16,47; 9,85</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 26,83</t>
+          <t>-15,85; 25,92</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-68,17; 47,23</t>
+          <t>-65,28; 59,37</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-35,39; 105,88</t>
+          <t>-34,57; 103,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-52,27; 158,55</t>
+          <t>-52,33; 149,79</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 33,37</t>
+          <t>-53,44; 24,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-55,28; 16,96</t>
+          <t>-55,19; 17,28</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-40,94; 78,17</t>
+          <t>-41,47; 84,83</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-50,0; 11,69</t>
+          <t>-48,74; 15,38</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-36,02; 25,96</t>
+          <t>-34,77; 29,1</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 72,24</t>
+          <t>-32,47; 66,85</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 17,1</t>
+          <t>0,06; 17,94</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 14,89</t>
+          <t>-3,73; 15,16</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 18,9</t>
+          <t>-10,11; 20,0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 6,09</t>
+          <t>-11,77; 6,82</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 4,46</t>
+          <t>-14,47; 4,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 11,28</t>
+          <t>-6,63; 12,18</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 8,71</t>
+          <t>-2,91; 9,81</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 7,25</t>
+          <t>-6,22; 6,66</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 12,08</t>
+          <t>-5,59; 11,91</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 61,31</t>
+          <t>0,13; 65,25</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 55,65</t>
+          <t>-10,11; 53,88</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 61,75</t>
+          <t>-27,65; 68,1</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 16,34</t>
+          <t>-25,37; 19,21</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 12,07</t>
+          <t>-30,94; 12,8</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 30,75</t>
+          <t>-14,43; 33,96</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 25,23</t>
+          <t>-7,25; 29,15</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 20,67</t>
+          <t>-15,27; 19,2</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 34,82</t>
+          <t>-13,95; 34,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 35,01</t>
+          <t>-19,89; 35,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 37,19</t>
+          <t>-17,18; 34,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 17,33</t>
+          <t>-31,3; 17,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 19,79</t>
+          <t>-36,67; 21,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 16,31</t>
+          <t>-42,81; 14,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 7,82</t>
+          <t>-55,44; 7,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 21,28</t>
+          <t>-20,33; 21,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 18,03</t>
+          <t>-23,77; 17,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 4,06</t>
+          <t>-34,44; 5,1</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 333,59</t>
+          <t>-52,52; 306,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,84; 332,02</t>
+          <t>-42,99; 328,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-78,68; 132,89</t>
+          <t>-74,04; 152,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,71; 66,4</t>
+          <t>-55,05; 66,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 52,39</t>
+          <t>-61,28; 46,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,14; 33,8</t>
+          <t>-80,94; 22,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,19; 82,06</t>
+          <t>-39,29; 81,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 70,77</t>
+          <t>-45,13; 67,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-70,05; 20,0</t>
+          <t>-68,4; 19,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 42,59</t>
+          <t>4,65; 46,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 34,17</t>
+          <t>-4,68; 34,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 58,89</t>
+          <t>-22,04; 59,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 39,93</t>
+          <t>-0,49; 39,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 41,16</t>
+          <t>-3,44; 39,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,71; 53,39</t>
+          <t>12,33; 53,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 37,31</t>
+          <t>7,63; 36,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 32,02</t>
+          <t>1,74; 32,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 47,83</t>
+          <t>-2,35; 47,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,69; 616,0</t>
+          <t>8,46; 634,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 460,64</t>
+          <t>-16,6; 493,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,58; 490,54</t>
+          <t>-49,43; 505,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 297,11</t>
+          <t>-0,69; 279,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 303,1</t>
+          <t>-7,84; 262,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,91; 430,0</t>
+          <t>28,02; 447,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,24; 266,61</t>
+          <t>25,96; 270,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 241,25</t>
+          <t>-0,95; 217,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 290,11</t>
+          <t>1,79; 293,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,9; 62,48</t>
+          <t>6,01; 59,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 47,53</t>
+          <t>-12,69; 47,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 36,81</t>
+          <t>-17,69; 36,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 28,97</t>
+          <t>-27,98; 27,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 27,61</t>
+          <t>-44,38; 27,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,83; -4,53</t>
+          <t>-56,37; -2,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 38,92</t>
+          <t>-3,61; 38,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 27,15</t>
+          <t>-19,44; 26,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,8; 10,64</t>
+          <t>-27,06; 11,68</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,15; 969,98</t>
+          <t>5,71; 943,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,52; —</t>
+          <t>-55,5; 731,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,27; 639,94</t>
+          <t>-48,61; 648,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,4; 147,25</t>
+          <t>-48,11; 125,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,07; 162,18</t>
+          <t>-82,19; 123,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-93,15; 1,85</t>
+          <t>-92,0; 21,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 243,18</t>
+          <t>-12,45; 202,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,51; 152,73</t>
+          <t>-49,46; 136,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,48; 71,26</t>
+          <t>-65,24; 73,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 19,22</t>
+          <t>-30,08; 22,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 26,36</t>
+          <t>-21,87; 26,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-24,89; 38,39</t>
+          <t>-26,14; 40,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-38,65; 19,25</t>
+          <t>-35,54; 22,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 17,45</t>
+          <t>-32,33; 15,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 56,52</t>
+          <t>-10,08; 53,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 13,96</t>
+          <t>-24,91; 12,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 14,52</t>
+          <t>-19,1; 16,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 38,68</t>
+          <t>-6,65; 39,9</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,15; 72,81</t>
+          <t>-53,36; 79,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,3; 102,13</t>
+          <t>-37,15; 112,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 146,07</t>
+          <t>-50,22; 152,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-68,71; 78,0</t>
+          <t>-64,93; 97,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,07; 66,89</t>
+          <t>-56,57; 58,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 238,47</t>
+          <t>-19,33; 214,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 43,71</t>
+          <t>-49,38; 40,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 49,35</t>
+          <t>-35,98; 54,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 120,76</t>
+          <t>-12,16; 129,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,35; 67,47</t>
+          <t>16,34; 70,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 53,08</t>
+          <t>-14,47; 52,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,41; 67,42</t>
+          <t>4,46; 67,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 42,85</t>
+          <t>-30,11; 43,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 45,22</t>
+          <t>-35,19; 40,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 42,57</t>
+          <t>-34,86; 44,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,78; 48,25</t>
+          <t>8,26; 53,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 34,74</t>
+          <t>-11,82; 41,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 44,92</t>
+          <t>-3,49; 45,3</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>35,74; —</t>
+          <t>33,31; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-97,01; —</t>
+          <t>-82,61; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,03; —</t>
+          <t>-1,21; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-49,41; 437,37</t>
+          <t>-51,55; 389,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,74; 397,03</t>
+          <t>-75,98; 353,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 325,08</t>
+          <t>-63,03; 326,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,81; 420,95</t>
+          <t>15,02; 483,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,64; 283,4</t>
+          <t>-39,34; 428,21</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 420,75</t>
+          <t>-11,35; 404,69</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 25,9</t>
+          <t>-37,82; 27,46</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 4,48</t>
+          <t>-54,14; 4,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 21,07</t>
+          <t>-46,31; 20,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-34,64; 30,33</t>
+          <t>-33,23; 27,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-58,01; -1,08</t>
+          <t>-59,32; -4,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-38,65; 27,27</t>
+          <t>-34,46; 26,92</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 19,61</t>
+          <t>-24,05; 18,76</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-47,12; -7,14</t>
+          <t>-48,14; -9,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 17,98</t>
+          <t>-28,13; 14,91</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-69,5; 134,75</t>
+          <t>-71,32; 144,87</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 59,46</t>
+          <t>-100,0; 34,65</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-84,99; 114,74</t>
+          <t>-87,85; 134,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-57,69; 127,59</t>
+          <t>-56,68; 119,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 71,46</t>
+          <t>-100,0; 21,86</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-61,8; 105,33</t>
+          <t>-60,89; 124,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-46,52; 71,42</t>
+          <t>-46,26; 67,55</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-93,14; -22,72</t>
+          <t>-92,57; -23,32</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 72,49</t>
+          <t>-57,72; 59,81</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 13,16</t>
+          <t>-31,0; 12,15</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 24,01</t>
+          <t>-24,19; 28,41</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 31,84</t>
+          <t>-14,49; 31,33</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-38,02; 4,02</t>
+          <t>-36,88; 5,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 31,89</t>
+          <t>-17,35; 34,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 23,03</t>
+          <t>-17,43; 26,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 3,71</t>
+          <t>-27,35; 3,78</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 23,07</t>
+          <t>-13,64; 24,0</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 22,09</t>
+          <t>-10,65; 21,69</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,22; 39,12</t>
+          <t>-50,2; 34,04</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-46,44; 63,94</t>
+          <t>-37,75; 78,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 90,29</t>
+          <t>-22,54; 94,18</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-72,29; 17,73</t>
+          <t>-71,08; 26,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-43,84; 104,73</t>
+          <t>-37,61; 116,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 78,76</t>
+          <t>-35,25; 88,58</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 10,32</t>
+          <t>-52,08; 11,24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 62,63</t>
+          <t>-25,95; 68,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 64,09</t>
+          <t>-20,68; 62,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 13,1</t>
+          <t>-28,86; 9,78</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 23,89</t>
+          <t>-13,78; 24,84</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 38,5</t>
+          <t>-19,78; 38,05</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 10,33</t>
+          <t>-30,08; 11,94</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 7,22</t>
+          <t>-29,61; 6,93</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 32,96</t>
+          <t>-20,9; 32,4</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 5,76</t>
+          <t>-23,43; 5,15</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 9,85</t>
+          <t>-18,06; 9,34</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 25,92</t>
+          <t>-13,85; 26,9</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-65,28; 59,37</t>
+          <t>-66,93; 44,24</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 103,16</t>
+          <t>-32,01; 102,82</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-52,33; 149,79</t>
+          <t>-49,54; 147,75</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-53,44; 24,49</t>
+          <t>-52,81; 29,39</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-55,19; 17,28</t>
+          <t>-54,95; 17,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-41,47; 84,83</t>
+          <t>-39,87; 81,36</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-48,74; 15,38</t>
+          <t>-48,2; 15,17</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-34,77; 29,1</t>
+          <t>-37,16; 26,54</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 66,85</t>
+          <t>-29,47; 72,04</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,06; 17,94</t>
+          <t>-0,03; 17,8</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 15,16</t>
+          <t>-3,18; 14,37</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 20,0</t>
+          <t>-11,52; 18,84</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 6,82</t>
+          <t>-10,18; 8,12</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 4,24</t>
+          <t>-14,51; 4,43</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 12,18</t>
+          <t>-8,29; 11,47</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 9,81</t>
+          <t>-3,6; 9,34</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 6,66</t>
+          <t>-5,94; 6,99</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 11,91</t>
+          <t>-5,9; 12,2</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0,13; 65,25</t>
+          <t>-0,2; 63,21</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 53,88</t>
+          <t>-8,35; 50,83</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 68,1</t>
+          <t>-29,72; 63,66</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 19,21</t>
+          <t>-22,33; 22,71</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 12,8</t>
+          <t>-31,73; 11,69</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 33,96</t>
+          <t>-18,43; 32,37</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 29,15</t>
+          <t>-8,95; 27,49</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 19,2</t>
+          <t>-14,66; 20,91</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 34,71</t>
+          <t>-13,6; 35,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-8,66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-12,85</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-26,22</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>8,49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11,19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,19</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-8,66</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-12,85</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-23,66</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-15,13</t>
+          <t>-12,93</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 35,28</t>
+          <t>-35,93; 20,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 34,88</t>
+          <t>-39,82; 15,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 17,5</t>
+          <t>-51,57; 5,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 21,15</t>
+          <t>-24,2; 32,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,81; 14,08</t>
+          <t>-17,71; 35,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 7,02</t>
+          <t>-25,8; 26,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 21,32</t>
+          <t>-19,4; 19,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 17,14</t>
+          <t>-20,78; 17,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 5,1</t>
+          <t>-31,04; 7,89</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-16,92%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-25,11%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-51,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>31,79%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>41,92%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-19,43%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-16,92%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-25,11%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-46,24%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-38,61%</t>
+          <t>-33,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,52; 306,38</t>
+          <t>-53,71; 68,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,99; 328,96</t>
+          <t>-59,87; 49,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,04; 152,69</t>
+          <t>-80,61; 21,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,05; 66,76</t>
+          <t>-56,36; 279,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,28; 46,66</t>
+          <t>-46,7; 308,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,94; 22,31</t>
+          <t>-62,11; 245,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,29; 81,54</t>
+          <t>-39,11; 73,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 67,22</t>
+          <t>-42,65; 66,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,4; 19,28</t>
+          <t>-62,36; 34,99</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21,24</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20,51</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33,83</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>25,27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>15,44</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21,74</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21,24</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,51</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,45</t>
+          <t>45,86</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>26,47</t>
+          <t>39,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 46,44</t>
+          <t>1,67; 40,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 34,67</t>
+          <t>-1,63; 43,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 59,67</t>
+          <t>11,95; 52,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 39,16</t>
+          <t>4,61; 44,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 39,25</t>
+          <t>-4,77; 34,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,33; 53,21</t>
+          <t>22,06; 64,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 36,01</t>
+          <t>8,58; 36,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 32,2</t>
+          <t>1,91; 32,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 47,21</t>
+          <t>23,88; 52,99</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83,33%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80,47%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>132,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>137,15%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>83,77%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>117,99%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>83,33%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>80,47%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>135,14%</t>
+          <t>248,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>118,91%</t>
+          <t>177,09%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 634,73</t>
+          <t>2,1; 303,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 493,18</t>
+          <t>-5,8; 328,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,43; 505,67</t>
+          <t>24,91; 408,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 279,92</t>
+          <t>7,88; 560,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 262,92</t>
+          <t>-19,19; 492,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,02; 447,46</t>
+          <t>64,94; 1044,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,96; 270,67</t>
+          <t>27,45; 266,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 217,21</t>
+          <t>4,72; 239,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 293,9</t>
+          <t>73,92; 386,61</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-9,83</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-29,27</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>37,84</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>16,53</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13,71</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-9,83</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-29,35</t>
+          <t>14,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,93</t>
+          <t>-7,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,01; 59,67</t>
+          <t>-32,92; 25,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 47,15</t>
+          <t>-43,22; 23,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 36,86</t>
+          <t>-55,7; -4,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 27,61</t>
+          <t>7,69; 60,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,38; 27,41</t>
+          <t>-17,18; 49,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,37; -2,46</t>
+          <t>-12,35; 37,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 38,44</t>
+          <t>-1,02; 37,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 26,98</t>
+          <t>-18,27; 29,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 11,68</t>
+          <t>-26,47; 12,68</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-0,97%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-23,75%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-70,74%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>196,78%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>85,98%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>71,3%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-0,97%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-23,75%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-70,92%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-26,63%</t>
+          <t>-24,18%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,71; 943,07</t>
+          <t>-52,64; 121,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,5; 731,32</t>
+          <t>-79,68; 121,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-48,61; 648,98</t>
+          <t>-92,35; 10,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,11; 125,74</t>
+          <t>7,45; 913,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,19; 123,56</t>
+          <t>-61,77; 897,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-92,0; 21,54</t>
+          <t>-40,56; 600,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 202,38</t>
+          <t>-3,01; 210,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 136,05</t>
+          <t>-50,54; 158,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 73,22</t>
+          <t>-62,4; 86,87</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-8,1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-7,77</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27,9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-4,75</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,74</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,47</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-8,1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-7,77</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16,15</t>
+          <t>15,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 22,06</t>
+          <t>-35,18; 22,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 26,55</t>
+          <t>-32,73; 18,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 40,3</t>
+          <t>-3,9; 56,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 22,59</t>
+          <t>-30,19; 21,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 15,31</t>
+          <t>-23,02; 27,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 53,74</t>
+          <t>-22,82; 34,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 12,6</t>
+          <t>-23,94; 14,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 16,47</t>
+          <t>-20,31; 15,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 39,9</t>
+          <t>-9,66; 39,67</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-19,15%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-18,36%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>65,94%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-10,97%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>4,02%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17,26%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-19,15%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-18,36%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-53,36; 79,25</t>
+          <t>-64,46; 88,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,15; 112,92</t>
+          <t>-58,16; 67,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,22; 152,27</t>
+          <t>-7,94; 227,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-64,93; 97,29</t>
+          <t>-52,38; 82,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,57; 58,76</t>
+          <t>-38,78; 111,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 214,02</t>
+          <t>-45,43; 128,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 40,76</t>
+          <t>-47,31; 46,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 54,41</t>
+          <t>-37,3; 50,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 129,24</t>
+          <t>-18,24; 121,33</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9,4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,57</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10,65</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>47,11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>18,86</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>39,66</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>40,0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22,26</t>
+          <t>25,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,34; 70,2</t>
+          <t>-27,85; 41,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 52,64</t>
+          <t>-34,92; 41,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,46; 67,11</t>
+          <t>-27,31; 46,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 43,19</t>
+          <t>15,18; 70,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 40,55</t>
+          <t>-13,42; 54,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 44,13</t>
+          <t>10,47; 69,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,26; 53,76</t>
+          <t>4,45; 50,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 41,13</t>
+          <t>-13,49; 36,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 45,3</t>
+          <t>-2,09; 48,75</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7,52%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>31,22%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>328,03%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>131,3%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>276,14%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>278,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>109,66%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>33,31; —</t>
+          <t>-50,72; 423,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-82,61; —</t>
+          <t>-74,88; 403,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-1,21; —</t>
+          <t>-52,39; 336,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 389,51</t>
+          <t>27,82; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,98; 353,84</t>
+          <t>-77,02; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-63,03; 326,92</t>
+          <t>2,03; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,02; 483,45</t>
+          <t>7,89; 543,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,34; 428,21</t>
+          <t>-43,7; 315,22</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 404,69</t>
+          <t>-7,5; 400,74</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-1,57</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-33,43</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-3,52</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-5,25</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-25,29</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-13,61</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,57</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-33,43</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,2</t>
+          <t>-13,0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-6,51</t>
+          <t>-6,98</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-37,82; 27,46</t>
+          <t>-32,43; 26,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 4,99</t>
+          <t>-59,78; -5,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-46,31; 20,55</t>
+          <t>-35,13; 24,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 27,27</t>
+          <t>-37,84; 24,8</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-59,32; -4,96</t>
+          <t>-50,98; 8,36</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 26,92</t>
+          <t>-42,21; 26,13</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 18,76</t>
+          <t>-23,19; 20,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-48,14; -9,66</t>
+          <t>-48,79; -8,19</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 14,91</t>
+          <t>-29,6; 14,96</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-3,75%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-80,05%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-8,42%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-13,37%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-64,46%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-34,68%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-3,75%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-80,05%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-7,67%</t>
+          <t>-33,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-16,12%</t>
+          <t>-17,27%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 144,87</t>
+          <t>-54,13; 125,41</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 34,65</t>
+          <t>-100,0; 33,42</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-87,85; 134,42</t>
+          <t>-62,15; 114,56</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-56,68; 119,47</t>
+          <t>-73,2; 114,36</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 21,86</t>
+          <t>-100,0; 100,46</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-60,89; 124,59</t>
+          <t>-82,44; 163,56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 67,55</t>
+          <t>-44,78; 92,65</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-92,57; -23,32</t>
+          <t>-93,12; -17,27</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-57,72; 59,81</t>
+          <t>-59,23; 50,67</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-15,6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>7,66</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2,83</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-8,31</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1,32</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>9,9</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-15,6</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>7,66</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>9,07</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>5,18</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 12,15</t>
+          <t>-35,14; 5,65</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 28,41</t>
+          <t>-18,76; 35,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 31,33</t>
+          <t>-21,4; 22,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 5,51</t>
+          <t>-32,67; 14,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 34,63</t>
+          <t>-23,99; 27,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 26,08</t>
+          <t>-13,24; 32,54</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 3,78</t>
+          <t>-27,16; 5,22</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 24,0</t>
+          <t>-14,31; 22,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 21,69</t>
+          <t>-11,1; 21,23</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-38,74%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>19,02%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-16,86%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2,68%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>20,08%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-38,74%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>19,02%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,2; 34,04</t>
+          <t>-69,45; 26,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 78,95</t>
+          <t>-36,76; 112,64</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 94,18</t>
+          <t>-41,79; 81,22</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-71,08; 26,15</t>
+          <t>-50,91; 46,96</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-37,61; 116,94</t>
+          <t>-40,43; 75,76</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-35,25; 88,58</t>
+          <t>-20,87; 98,22</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-52,08; 11,24</t>
+          <t>-51,89; 14,11</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 68,15</t>
+          <t>-27,79; 59,43</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 62,11</t>
+          <t>-20,8; 58,95</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-8,77</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-11,7</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>4,71</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-8,71</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>5,28</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>6,33</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-8,77</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-11,7</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>6,11</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>5,25</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-28,86; 9,78</t>
+          <t>-28,2; 12,57</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 24,84</t>
+          <t>-29,48; 7,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 38,05</t>
+          <t>-23,38; 31,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 11,94</t>
+          <t>-29,93; 11,9</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 6,93</t>
+          <t>-14,16; 24,22</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 32,4</t>
+          <t>-21,47; 42,04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 5,15</t>
+          <t>-24,22; 4,15</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 9,34</t>
+          <t>-17,02; 9,26</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 26,9</t>
+          <t>-14,96; 27,28</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-18,47%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-24,66%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-25,04%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>15,17%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-18,47%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-24,66%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-66,93; 44,24</t>
+          <t>-51,07; 33,37</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 102,82</t>
+          <t>-55,28; 16,96</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 147,75</t>
+          <t>-42,5; 77,81</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-52,81; 29,39</t>
+          <t>-68,17; 47,23</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-54,95; 17,37</t>
+          <t>-35,39; 105,88</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 81,36</t>
+          <t>-54,49; 158,54</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 15,17</t>
+          <t>-50,0; 11,69</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-37,16; 26,54</t>
+          <t>-36,02; 25,96</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 72,04</t>
+          <t>-31,67; 74,19</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-2,21</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-4,49</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2,74</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>8,99</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>5,74</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>7,29</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-2,21</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-4,49</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>15,75</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>8,79</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 17,8</t>
+          <t>-10,88; 6,09</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 14,37</t>
+          <t>-13,99; 4,46</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 18,84</t>
+          <t>-6,81; 11,15</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 8,12</t>
+          <t>-0,53; 17,1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 4,43</t>
+          <t>-2,4; 14,89</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 11,47</t>
+          <t>5,79; 24,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 9,34</t>
+          <t>-3,55; 8,71</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 6,99</t>
+          <t>-5,98; 7,25</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 12,2</t>
+          <t>2,44; 15,27</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-5,36%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-10,89%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>27,29%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>17,41%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-5,36%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-10,89%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 63,21</t>
+          <t>-24,42; 16,34</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 50,83</t>
+          <t>-31,09; 12,07</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 63,66</t>
+          <t>-15,78; 31,04</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 22,71</t>
+          <t>-1,21; 61,31</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 11,69</t>
+          <t>-6,92; 55,65</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 32,37</t>
+          <t>16,42; 90,06</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 27,49</t>
+          <t>-8,5; 25,23</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 20,91</t>
+          <t>-14,85; 20,67</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 35,18</t>
+          <t>6,13; 46,06</t>
         </is>
       </c>
     </row>
